--- a/XLibur.Tests/Resource/Other/Formulas/DataTableFormula-Output.xlsx
+++ b/XLibur.Tests/Resource/Other/Formulas/DataTableFormula-Output.xlsx
@@ -501,6 +501,7 @@
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <x:c r="C3" s="0">
         <x:f>A1*10</x:f>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -509,6 +510,7 @@
       </x:c>
       <x:c r="C4" s="0">
         <x:f t="dataTable" ref="C4:C8" r1="A1" ca="1"/>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,11 +590,13 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <x:c r="B4" s="0">
+      <x:c r="B4" s="0" t="str">
         <x:f>REPT(A1,2)</x:f>
-      </x:c>
-      <x:c r="C4" s="0">
+        <x:v>ZZ</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="str">
         <x:f t="dataTable" ref="C4:G4" dtr="1" r1="A1" ca="1"/>
+        <x:v>AA</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>8</x:v>
@@ -630,8 +634,9 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="B4" s="0">
+      <x:c r="B4" s="0" t="str">
         <x:f>B7 &amp; B8</x:f>
+        <x:v>A1</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>10</x:v>
@@ -641,8 +646,9 @@
       <x:c r="B5" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="0">
+      <x:c r="C5" s="0" t="str">
         <x:f t="dataTable" ref="C5" dt2D="1" r1="B8" r2="B7" ca="1"/>
+        <x:v>Z10</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -695,8 +701,9 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="B4" s="1">
+      <x:c r="B4" s="1" t="str">
         <x:f>B1 &amp; B2</x:f>
+        <x:v>Z1</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>2</x:v>
@@ -709,8 +716,9 @@
       <x:c r="B5" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="0">
+      <x:c r="C5" s="0" t="str">
         <x:f t="dataTable" ref="C5:D8" dt2D="1" r1="B2" r2="B1" ca="1"/>
+        <x:v>A2</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>15</x:v>
@@ -767,16 +775,18 @@
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:sheetData>
     <x:row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="C2" s="0">
+      <x:c r="C2" s="0" t="e">
         <x:f>#REF!*3</x:f>
+        <x:v>#REF!</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <x:c r="B3" s="0">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C3" s="0">
-        <x:f t="dataTable" ref="C3:C5" dtr="1" del1="1" r1="B1" ca="1"/>
+      <x:c r="C3" s="0" t="e">
+        <x:f t="dataTable" ref="C3:C5" dtr="1" r1="B1" del1="1" ca="1"/>
+        <x:v>#REF!</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -835,11 +845,13 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A4" s="0">
+      <x:c r="A4" s="0" t="e">
         <x:f>REPT(#REF!,2)</x:f>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:f t="dataTable" ref="B4:F4" dtr="1" del1="1" r1="A1" ca="1"/>
+        <x:v>#REF!</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="e">
+        <x:f t="dataTable" ref="B4:F4" dtr="1" r1="A1" del1="1" ca="1"/>
+        <x:v>#REF!</x:v>
       </x:c>
       <x:c r="C4" s="0" t="e">
         <x:v>#REF!</x:v>
@@ -877,8 +889,9 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="C3" s="0">
+      <x:c r="C3" s="0" t="e">
         <x:f>A1&amp;#REF!</x:f>
+        <x:v>#REF!</x:v>
       </x:c>
       <x:c r="D3" s="0">
         <x:v>1</x:v>
@@ -891,8 +904,9 @@
       <x:c r="C4" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D4" s="0">
-        <x:f t="dataTable" ref="D4:E6" dt2D="1" del1="1" r1="A2" r2="A1" ca="1"/>
+      <x:c r="D4" s="0" t="e">
+        <x:f t="dataTable" ref="D4:E6" dt2D="1" r1="A2" del1="1" r2="A1" ca="1"/>
+        <x:v>#REF!</x:v>
       </x:c>
       <x:c r="E4" s="0" t="e">
         <x:v>#REF!</x:v>
@@ -943,8 +957,9 @@
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="B2" s="0">
+      <x:c r="B2" s="0" t="e">
         <x:f>#REF!&amp;A1</x:f>
+        <x:v>#REF!</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>1</x:v>
@@ -957,8 +972,9 @@
       <x:c r="B3" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C3" s="0">
-        <x:f t="dataTable" ref="C3:D5" dt2D="1" del2="1" r1="A1" r2="A1" ca="1"/>
+      <x:c r="C3" s="0" t="e">
+        <x:f t="dataTable" ref="C3:D5" dt2D="1" r1="A1" r2="A1" del2="1" ca="1"/>
+        <x:v>#REF!</x:v>
       </x:c>
       <x:c r="D3" s="0" t="e">
         <x:v>#REF!</x:v>
@@ -1004,8 +1020,9 @@
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:sheetData>
     <x:row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="B1" s="0">
+      <x:c r="B1" s="0" t="e">
         <x:f>#REF!&amp;#REF!</x:f>
+        <x:v>#REF!</x:v>
       </x:c>
       <x:c r="C1" s="0">
         <x:v>1</x:v>
@@ -1018,8 +1035,9 @@
       <x:c r="B2" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C2" s="0">
-        <x:f t="dataTable" ref="C2:D4" dt2D="1" del1="1" del2="1" r1="A2" r2="A1" ca="1"/>
+      <x:c r="C2" s="0" t="e">
+        <x:f t="dataTable" ref="C2:D4" dt2D="1" r1="A2" del1="1" r2="A1" del2="1" ca="1"/>
+        <x:v>#REF!</x:v>
       </x:c>
       <x:c r="D2" s="0" t="e">
         <x:v>#REF!</x:v>
